--- a/SelecciónDatasetsProyecto/CLIMA_CANARIAS/CLIMA_CANARIAS_metadatos.xlsx
+++ b/SelecciónDatasetsProyecto/CLIMA_CANARIAS/CLIMA_CANARIAS_metadatos.xlsx
@@ -62,7 +62,7 @@
     <t xml:space="preserve">Fecha.de.generacion</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28</t>
+    <t xml:space="preserve">2026-10-08</t>
   </si>
   <si>
     <t xml:space="preserve">Fichero.observaciones</t>
